--- a/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="38">
   <si>
     <t>Apellido y Nombre</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>Evaluación 3</t>
+  </si>
+  <si>
+    <t>Evaluación 4</t>
   </si>
 </sst>
 </file>
@@ -177,7 +180,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -220,6 +223,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -233,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -244,19 +253,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -539,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:R14"/>
+  <dimension ref="B1:T14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
@@ -556,38 +568,44 @@
     <col min="14" max="14" width="15.85546875" customWidth="1"/>
     <col min="16" max="16" width="11.28515625" customWidth="1"/>
     <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="14" t="s">
+    <row r="1" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="10" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="G1" s="13" t="s">
+      <c r="E1" s="13"/>
+      <c r="G1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="J1" s="13" t="s">
+      <c r="H1" s="12"/>
+      <c r="J1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="12" t="s">
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="10" t="s">
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-    </row>
-    <row r="2" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="T1" s="15"/>
+    </row>
+    <row r="2" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -620,7 +638,7 @@
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
     </row>
-    <row r="3" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K3" s="1" t="s">
         <v>27</v>
       </c>
@@ -633,8 +651,11 @@
       <c r="Q3" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="T3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
@@ -671,8 +692,11 @@
       <c r="Q4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2</v>
       </c>
@@ -709,8 +733,14 @@
       <c r="Q5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S5" t="s">
+        <v>16</v>
+      </c>
+      <c r="T5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>3</v>
       </c>
@@ -750,8 +780,14 @@
       <c r="Q6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>4</v>
       </c>
@@ -788,8 +824,14 @@
       <c r="Q7" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S7" t="s">
+        <v>16</v>
+      </c>
+      <c r="T7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B8" s="9">
         <v>5</v>
       </c>
@@ -825,8 +867,11 @@
       <c r="Q8" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>6</v>
       </c>
@@ -860,8 +905,14 @@
       <c r="Q9" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S9" t="s">
+        <v>16</v>
+      </c>
+      <c r="T9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>7</v>
       </c>
@@ -901,8 +952,11 @@
       <c r="Q10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>8</v>
       </c>
@@ -936,8 +990,11 @@
       <c r="Q11" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>9</v>
       </c>
@@ -974,8 +1031,11 @@
       <c r="Q12" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S12" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>10</v>
       </c>
@@ -1012,8 +1072,14 @@
       <c r="Q13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S13" t="s">
+        <v>16</v>
+      </c>
+      <c r="T13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>11</v>
       </c>
@@ -1050,10 +1116,14 @@
       <c r="Q14" s="7" t="s">
         <v>25</v>
       </c>
+      <c r="S14" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B2:H14"/>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="S1:T1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="J1:L1"/>

--- a/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$2:$H$14</definedName>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="40">
   <si>
     <t>Apellido y Nombre</t>
   </si>
@@ -136,6 +137,12 @@
   </si>
   <si>
     <t>Evaluación 4</t>
+  </si>
+  <si>
+    <t>QUINTEROS GABRIEL</t>
+  </si>
+  <si>
+    <t>CORIA MARCOS</t>
   </si>
 </sst>
 </file>
@@ -253,6 +260,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -266,9 +276,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -573,37 +580,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="13" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="G1" s="12" t="s">
+      <c r="E1" s="14"/>
+      <c r="G1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="12"/>
-      <c r="J1" s="12" t="s">
+      <c r="H1" s="13"/>
+      <c r="J1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="14" t="s">
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="13" t="s">
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="15" t="s">
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T1" s="15"/>
+      <c r="T1" s="10"/>
     </row>
     <row r="2" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -624,19 +631,19 @@
       <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11" t="s">
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
     </row>
     <row r="3" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K3" s="1" t="s">
@@ -1137,4 +1144,33 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>